--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040137</v>
+        <v>120040197</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477961</v>
+        <v>477985</v>
       </c>
       <c r="R2" t="n">
-        <v>7068788</v>
+        <v>7068683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040198</v>
+        <v>120040196</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478016</v>
+        <v>477986</v>
       </c>
       <c r="R3" t="n">
-        <v>7068671</v>
+        <v>7068766</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040195</v>
+        <v>120040198</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478013</v>
+        <v>478016</v>
       </c>
       <c r="R5" t="n">
-        <v>7068772</v>
+        <v>7068671</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040196</v>
+        <v>120040195</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477986</v>
+        <v>478013</v>
       </c>
       <c r="R7" t="n">
-        <v>7068766</v>
+        <v>7068772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040197</v>
+        <v>120040137</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477985</v>
+        <v>477961</v>
       </c>
       <c r="R8" t="n">
-        <v>7068683</v>
+        <v>7068788</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040197</v>
+        <v>120040198</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477985</v>
+        <v>478016</v>
       </c>
       <c r="R2" t="n">
-        <v>7068683</v>
+        <v>7068671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040196</v>
+        <v>120040137</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477986</v>
+        <v>477961</v>
       </c>
       <c r="R3" t="n">
-        <v>7068766</v>
+        <v>7068788</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040193</v>
+        <v>120040196</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478023</v>
+        <v>477986</v>
       </c>
       <c r="R4" t="n">
-        <v>7068787</v>
+        <v>7068766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040198</v>
+        <v>120040178</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478016</v>
+        <v>478132</v>
       </c>
       <c r="R5" t="n">
-        <v>7068671</v>
+        <v>7068686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040178</v>
+        <v>120040195</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478132</v>
+        <v>478013</v>
       </c>
       <c r="R6" t="n">
-        <v>7068686</v>
+        <v>7068772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040195</v>
+        <v>120040193</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478013</v>
+        <v>478023</v>
       </c>
       <c r="R7" t="n">
-        <v>7068772</v>
+        <v>7068787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040137</v>
+        <v>120040197</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477961</v>
+        <v>477985</v>
       </c>
       <c r="R8" t="n">
-        <v>7068788</v>
+        <v>7068683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040198</v>
+        <v>120040193</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478016</v>
+        <v>478023</v>
       </c>
       <c r="R2" t="n">
-        <v>7068671</v>
+        <v>7068787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040137</v>
+        <v>120040195</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477961</v>
+        <v>478013</v>
       </c>
       <c r="R3" t="n">
-        <v>7068788</v>
+        <v>7068772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040196</v>
+        <v>120040178</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477986</v>
+        <v>478132</v>
       </c>
       <c r="R4" t="n">
-        <v>7068766</v>
+        <v>7068686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040178</v>
+        <v>120040196</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478132</v>
+        <v>477986</v>
       </c>
       <c r="R5" t="n">
-        <v>7068686</v>
+        <v>7068766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040195</v>
+        <v>120040137</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478013</v>
+        <v>477961</v>
       </c>
       <c r="R6" t="n">
-        <v>7068772</v>
+        <v>7068788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040193</v>
+        <v>120040197</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478023</v>
+        <v>477985</v>
       </c>
       <c r="R7" t="n">
-        <v>7068787</v>
+        <v>7068683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040197</v>
+        <v>120040198</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477985</v>
+        <v>478016</v>
       </c>
       <c r="R8" t="n">
-        <v>7068683</v>
+        <v>7068671</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120040193</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040195</v>
+        <v>120040197</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478013</v>
+        <v>477985</v>
       </c>
       <c r="R3" t="n">
-        <v>7068772</v>
+        <v>7068683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040178</v>
+        <v>120040137</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478132</v>
+        <v>477961</v>
       </c>
       <c r="R4" t="n">
-        <v>7068686</v>
+        <v>7068788</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040196</v>
+        <v>120040178</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477986</v>
+        <v>478132</v>
       </c>
       <c r="R5" t="n">
-        <v>7068766</v>
+        <v>7068686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040137</v>
+        <v>120040195</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477961</v>
+        <v>478013</v>
       </c>
       <c r="R6" t="n">
-        <v>7068788</v>
+        <v>7068772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040197</v>
+        <v>120040198</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477985</v>
+        <v>478016</v>
       </c>
       <c r="R7" t="n">
-        <v>7068683</v>
+        <v>7068671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040198</v>
+        <v>120040196</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478016</v>
+        <v>477986</v>
       </c>
       <c r="R8" t="n">
-        <v>7068671</v>
+        <v>7068766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040193</v>
+        <v>120040137</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478023</v>
+        <v>477961</v>
       </c>
       <c r="R2" t="n">
-        <v>7068787</v>
+        <v>7068788</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040197</v>
+        <v>120040178</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477985</v>
+        <v>478132</v>
       </c>
       <c r="R3" t="n">
-        <v>7068683</v>
+        <v>7068686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040137</v>
+        <v>120040193</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477961</v>
+        <v>478023</v>
       </c>
       <c r="R4" t="n">
-        <v>7068788</v>
+        <v>7068787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040178</v>
+        <v>120040197</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478132</v>
+        <v>477985</v>
       </c>
       <c r="R5" t="n">
-        <v>7068686</v>
+        <v>7068683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040137</v>
+        <v>120040196</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477961</v>
+        <v>477986</v>
       </c>
       <c r="R2" t="n">
-        <v>7068788</v>
+        <v>7068766</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040178</v>
+        <v>120040193</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478132</v>
+        <v>478023</v>
       </c>
       <c r="R3" t="n">
-        <v>7068686</v>
+        <v>7068787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040193</v>
+        <v>120040198</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478023</v>
+        <v>478016</v>
       </c>
       <c r="R4" t="n">
-        <v>7068787</v>
+        <v>7068671</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040197</v>
+        <v>120040137</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477985</v>
+        <v>477961</v>
       </c>
       <c r="R5" t="n">
-        <v>7068683</v>
+        <v>7068788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040195</v>
+        <v>120040178</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478013</v>
+        <v>478132</v>
       </c>
       <c r="R6" t="n">
-        <v>7068772</v>
+        <v>7068686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040198</v>
+        <v>120040195</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478016</v>
+        <v>478013</v>
       </c>
       <c r="R7" t="n">
-        <v>7068671</v>
+        <v>7068772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040196</v>
+        <v>120040197</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477986</v>
+        <v>477985</v>
       </c>
       <c r="R8" t="n">
-        <v>7068766</v>
+        <v>7068683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040196</v>
+        <v>120040197</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477986</v>
+        <v>477985</v>
       </c>
       <c r="R2" t="n">
-        <v>7068766</v>
+        <v>7068683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040193</v>
+        <v>120040195</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478023</v>
+        <v>478013</v>
       </c>
       <c r="R3" t="n">
-        <v>7068787</v>
+        <v>7068772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040198</v>
+        <v>120040137</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478016</v>
+        <v>477961</v>
       </c>
       <c r="R4" t="n">
-        <v>7068671</v>
+        <v>7068788</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040137</v>
+        <v>120040193</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477961</v>
+        <v>478023</v>
       </c>
       <c r="R5" t="n">
-        <v>7068788</v>
+        <v>7068787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040195</v>
+        <v>120040198</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478013</v>
+        <v>478016</v>
       </c>
       <c r="R7" t="n">
-        <v>7068772</v>
+        <v>7068671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040197</v>
+        <v>120040196</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477985</v>
+        <v>477986</v>
       </c>
       <c r="R8" t="n">
-        <v>7068683</v>
+        <v>7068766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040197</v>
+        <v>120040193</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477985</v>
+        <v>478023</v>
       </c>
       <c r="R2" t="n">
-        <v>7068683</v>
+        <v>7068787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040195</v>
+        <v>120040197</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478013</v>
+        <v>477985</v>
       </c>
       <c r="R3" t="n">
-        <v>7068772</v>
+        <v>7068683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040137</v>
+        <v>120040196</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477961</v>
+        <v>477986</v>
       </c>
       <c r="R4" t="n">
-        <v>7068788</v>
+        <v>7068766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040193</v>
+        <v>120040137</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478023</v>
+        <v>477961</v>
       </c>
       <c r="R5" t="n">
-        <v>7068787</v>
+        <v>7068788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040196</v>
+        <v>120040195</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477986</v>
+        <v>478013</v>
       </c>
       <c r="R8" t="n">
-        <v>7068766</v>
+        <v>7068772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040197</v>
+        <v>120040196</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477985</v>
+        <v>477986</v>
       </c>
       <c r="R3" t="n">
-        <v>7068683</v>
+        <v>7068766</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040196</v>
+        <v>120040137</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477986</v>
+        <v>477961</v>
       </c>
       <c r="R4" t="n">
-        <v>7068766</v>
+        <v>7068788</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040137</v>
+        <v>120040198</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477961</v>
+        <v>478016</v>
       </c>
       <c r="R5" t="n">
-        <v>7068788</v>
+        <v>7068671</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040198</v>
+        <v>120040197</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478016</v>
+        <v>477985</v>
       </c>
       <c r="R7" t="n">
-        <v>7068671</v>
+        <v>7068683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040193</v>
+        <v>120040198</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478023</v>
+        <v>478016</v>
       </c>
       <c r="R2" t="n">
-        <v>7068787</v>
+        <v>7068671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040196</v>
+        <v>120040193</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477986</v>
+        <v>478023</v>
       </c>
       <c r="R3" t="n">
-        <v>7068766</v>
+        <v>7068787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040137</v>
+        <v>120040178</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477961</v>
+        <v>478132</v>
       </c>
       <c r="R4" t="n">
-        <v>7068788</v>
+        <v>7068686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040198</v>
+        <v>120040197</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478016</v>
+        <v>477985</v>
       </c>
       <c r="R5" t="n">
-        <v>7068671</v>
+        <v>7068683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040178</v>
+        <v>120040137</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478132</v>
+        <v>477961</v>
       </c>
       <c r="R6" t="n">
-        <v>7068686</v>
+        <v>7068788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040197</v>
+        <v>120040195</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477985</v>
+        <v>478013</v>
       </c>
       <c r="R7" t="n">
-        <v>7068683</v>
+        <v>7068772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040195</v>
+        <v>120040196</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478013</v>
+        <v>477986</v>
       </c>
       <c r="R8" t="n">
-        <v>7068772</v>
+        <v>7068766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040198</v>
+        <v>120040178</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478016</v>
+        <v>478132</v>
       </c>
       <c r="R2" t="n">
-        <v>7068671</v>
+        <v>7068686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120040193</v>
+        <v>120040137</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478023</v>
+        <v>477961</v>
       </c>
       <c r="R3" t="n">
-        <v>7068787</v>
+        <v>7068788</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040178</v>
+        <v>120040196</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478132</v>
+        <v>477986</v>
       </c>
       <c r="R4" t="n">
-        <v>7068686</v>
+        <v>7068766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040197</v>
+        <v>120040195</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477985</v>
+        <v>478013</v>
       </c>
       <c r="R5" t="n">
-        <v>7068683</v>
+        <v>7068772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040137</v>
+        <v>120040193</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477961</v>
+        <v>478023</v>
       </c>
       <c r="R6" t="n">
-        <v>7068788</v>
+        <v>7068787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040195</v>
+        <v>120040197</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478013</v>
+        <v>477985</v>
       </c>
       <c r="R7" t="n">
-        <v>7068772</v>
+        <v>7068683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120040196</v>
+        <v>120040198</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477986</v>
+        <v>478016</v>
       </c>
       <c r="R8" t="n">
-        <v>7068766</v>
+        <v>7068671</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120040196</v>
+        <v>120040137</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477986</v>
+        <v>477961</v>
       </c>
       <c r="R2" t="n">
-        <v>7068766</v>
+        <v>7068788</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +780,7 @@
         <v>120040178</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120040197</v>
+        <v>120040193</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477985</v>
+        <v>478023</v>
       </c>
       <c r="R4" t="n">
-        <v>7068683</v>
+        <v>7068787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120040137</v>
+        <v>120040195</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477961</v>
+        <v>478013</v>
       </c>
       <c r="R5" t="n">
-        <v>7068788</v>
+        <v>7068772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120040193</v>
+        <v>120040196</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478023</v>
+        <v>477986</v>
       </c>
       <c r="R6" t="n">
-        <v>7068787</v>
+        <v>7068766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120040195</v>
+        <v>120040197</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478013</v>
+        <v>477985</v>
       </c>
       <c r="R7" t="n">
-        <v>7068772</v>
+        <v>7068683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,12 +1270,7 @@
         <v>120040198</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40236-2024 artfynd.xlsx
+++ b/artfynd/A 40236-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,8 +1396,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120040198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>